--- a/Data/FlightPlan/FPL_07SEP26.xlsx
+++ b/Data/FlightPlan/FPL_07SEP26.xlsx
@@ -176,6 +176,9 @@
     <t>09:35</t>
   </si>
   <si>
+    <t>09:36</t>
+  </si>
+  <si>
     <t>HPH</t>
   </si>
   <si>
@@ -419,6 +422,9 @@
     <t>08:20</t>
   </si>
   <si>
+    <t>10:05</t>
+  </si>
+  <si>
     <t>10:45</t>
   </si>
   <si>
@@ -479,6 +485,9 @@
     <t>07:00</t>
   </si>
   <si>
+    <t>07:04</t>
+  </si>
+  <si>
     <t>07:30</t>
   </si>
   <si>
@@ -521,6 +530,9 @@
     <t>08:45</t>
   </si>
   <si>
+    <t>09:15</t>
+  </si>
+  <si>
     <t>BLR</t>
   </si>
   <si>
@@ -560,6 +572,9 @@
     <t>06:25</t>
   </si>
   <si>
+    <t>08:51</t>
+  </si>
+  <si>
     <t>929 *</t>
   </si>
   <si>
@@ -593,6 +608,9 @@
     <t>05:00</t>
   </si>
   <si>
+    <t>07:02</t>
+  </si>
+  <si>
     <t>08:10</t>
   </si>
   <si>
@@ -638,6 +656,9 @@
     <t>09:40</t>
   </si>
   <si>
+    <t>09:44</t>
+  </si>
+  <si>
     <t>18:15</t>
   </si>
   <si>
@@ -656,6 +677,9 @@
     <t>04:40</t>
   </si>
   <si>
+    <t>08:25</t>
+  </si>
+  <si>
     <t>03:10</t>
   </si>
   <si>
@@ -728,6 +752,9 @@
     <t>09:55</t>
   </si>
   <si>
+    <t>09:21</t>
+  </si>
+  <si>
     <t>MFM</t>
   </si>
   <si>
@@ -740,7 +767,7 @@
     <t>VN-A632</t>
   </si>
   <si>
-    <t>09:15</t>
+    <t>06:32</t>
   </si>
   <si>
     <t>15:40</t>
@@ -773,6 +800,9 @@
     <t>VN-A634</t>
   </si>
   <si>
+    <t>08:04</t>
+  </si>
+  <si>
     <t>11:30</t>
   </si>
   <si>
@@ -794,6 +824,9 @@
     <t>07:05</t>
   </si>
   <si>
+    <t>07:09</t>
+  </si>
+  <si>
     <t>KUL</t>
   </si>
   <si>
@@ -818,6 +851,9 @@
     <t>VN-A639</t>
   </si>
   <si>
+    <t>07:24</t>
+  </si>
+  <si>
     <t>13:55</t>
   </si>
   <si>
@@ -839,6 +875,9 @@
     <t>07:40</t>
   </si>
   <si>
+    <t>07:36</t>
+  </si>
+  <si>
     <t>08:40</t>
   </si>
   <si>
@@ -860,6 +899,9 @@
     <t>06:20</t>
   </si>
   <si>
+    <t>06:17</t>
+  </si>
+  <si>
     <t>09:45</t>
   </si>
   <si>
@@ -935,6 +977,9 @@
     <t>VN-A649</t>
   </si>
   <si>
+    <t>07:39</t>
+  </si>
+  <si>
     <t>17:40</t>
   </si>
   <si>
@@ -986,6 +1031,9 @@
     <t>VN-A656</t>
   </si>
   <si>
+    <t>06:57</t>
+  </si>
+  <si>
     <t>VN-A657</t>
   </si>
   <si>
@@ -1001,6 +1049,9 @@
     <t>05:20</t>
   </si>
   <si>
+    <t>06:34</t>
+  </si>
+  <si>
     <t>21:55</t>
   </si>
   <si>
@@ -1019,6 +1070,9 @@
     <t>05:45</t>
   </si>
   <si>
+    <t>07:27</t>
+  </si>
+  <si>
     <t>08:05</t>
   </si>
   <si>
@@ -1049,9 +1103,6 @@
     <t>08:35</t>
   </si>
   <si>
-    <t>10:05</t>
-  </si>
-  <si>
     <t>17:05</t>
   </si>
   <si>
@@ -1061,6 +1112,9 @@
     <t>06:05</t>
   </si>
   <si>
+    <t>07:34</t>
+  </si>
+  <si>
     <t>VN-A673</t>
   </si>
   <si>
@@ -1121,9 +1175,6 @@
     <t>VN-A689</t>
   </si>
   <si>
-    <t>08:25</t>
-  </si>
-  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1145,6 +1196,9 @@
     <t>VN-A811</t>
   </si>
   <si>
+    <t>06:49</t>
+  </si>
+  <si>
     <t>UFA</t>
   </si>
   <si>
@@ -1187,7 +1241,7 @@
     <t>Total Record(s): 374</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 06, 2026 22:15</t>
+    <t xml:space="preserve">Generated on  Sep 07, 2026 06:15</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2274,7 +2328,9 @@
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
+      <c t="s" r="M24" s="7">
+        <v>55</v>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c t="s" r="A25" s="6">
@@ -2297,13 +2353,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H25" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2327,16 +2383,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G26" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H26" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2366,10 +2422,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2396,13 +2452,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H28" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2426,7 +2482,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G29" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="H29" s="8">
         <v>22</v>
@@ -2435,7 +2491,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2468,7 +2524,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2477,13 +2533,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H31" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2501,19 +2557,19 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G32" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H32" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J32" s="7">
         <v>28</v>
@@ -2534,7 +2590,7 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
@@ -2543,13 +2599,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H33" s="8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2582,19 +2638,19 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G35" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H35" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J35" s="7">
         <v>23</v>
@@ -2615,7 +2671,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2624,13 +2680,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H36" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2648,22 +2704,22 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H37" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2696,7 +2752,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2705,13 +2761,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2729,19 +2785,19 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="H40" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J40" s="7">
         <v>39</v>
@@ -2762,7 +2818,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2771,13 +2827,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2795,22 +2851,22 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2843,7 +2899,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -2852,13 +2908,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2876,22 +2932,22 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -2909,7 +2965,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2918,13 +2974,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2942,22 +2998,22 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2990,13 +3046,13 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>22</v>
@@ -3005,7 +3061,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3023,7 +3079,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3035,10 +3091,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3056,7 +3112,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3068,10 +3124,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3089,7 +3145,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3098,13 +3154,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3137,7 +3193,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3149,14 +3205,16 @@
         <v>27</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
+      <c t="s" r="M54" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c t="s" r="A55" s="6">
@@ -3170,7 +3228,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3182,7 +3240,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J55" s="7">
         <v>54</v>
@@ -3203,7 +3261,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3212,13 +3270,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3236,22 +3294,22 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3269,7 +3327,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3278,13 +3336,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3302,22 +3360,22 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3335,7 +3393,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3347,10 +3405,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3383,13 +3441,13 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>22</v>
@@ -3398,7 +3456,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3416,7 +3474,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3428,10 +3486,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3449,7 +3507,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3461,10 +3519,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3497,7 +3555,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3506,13 +3564,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3530,22 +3588,22 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3563,7 +3621,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3575,10 +3633,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3596,7 +3654,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3611,7 +3669,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3629,7 +3687,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3641,10 +3699,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3677,7 +3735,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3686,17 +3744,21 @@
         <v>22</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="I72" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>134</v>
-      </c>
-      <c r="K72" s="7"/>
+        <v>135</v>
+      </c>
+      <c t="s" r="K72" s="7">
+        <v>45</v>
+      </c>
       <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
+      <c t="s" r="M72" s="7">
+        <v>136</v>
+      </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c t="s" r="A73" s="6">
@@ -3710,26 +3772,30 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>20</v>
       </c>
-      <c r="K73" s="7"/>
+      <c t="s" r="K73" s="7">
+        <v>19</v>
+      </c>
       <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
+      <c t="s" r="M73" s="7">
+        <v>137</v>
+      </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c t="s" r="A74" s="6">
@@ -3743,7 +3809,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3752,13 +3818,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3776,22 +3842,22 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3809,7 +3875,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3821,10 +3887,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3842,7 +3908,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3854,10 +3920,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3890,7 +3956,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -3902,14 +3968,16 @@
         <v>27</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
+      <c t="s" r="M79" s="7">
+        <v>48</v>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c t="s" r="A80" s="6">
@@ -3923,7 +3991,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3935,10 +4003,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3956,7 +4024,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -3965,13 +4033,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -3989,22 +4057,22 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4022,7 +4090,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4031,13 +4099,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4055,22 +4123,22 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4103,7 +4171,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4112,17 +4180,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
+      <c t="s" r="M86" s="7">
+        <v>158</v>
+      </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c t="s" r="A87" s="6">
@@ -4136,22 +4206,22 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4169,7 +4239,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4178,13 +4248,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4202,22 +4272,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4235,7 +4305,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4244,13 +4314,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4268,22 +4338,22 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4301,7 +4371,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4313,10 +4383,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4334,7 +4404,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4346,10 +4416,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4382,7 +4452,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4391,13 +4461,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4415,19 +4485,19 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>38</v>
@@ -4448,7 +4518,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4460,10 +4530,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4481,7 +4551,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4493,10 +4563,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4529,7 +4599,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4538,17 +4608,21 @@
         <v>22</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>49</v>
       </c>
-      <c r="K100" s="7"/>
+      <c t="s" r="K100" s="7">
+        <v>173</v>
+      </c>
       <c r="L100" s="7"/>
-      <c r="M100" s="7"/>
+      <c t="s" r="M100" s="7">
+        <v>110</v>
+      </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c t="s" r="A101" s="6">
@@ -4562,22 +4636,22 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4595,7 +4669,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4604,13 +4678,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4628,22 +4702,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4676,7 +4750,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4685,13 +4759,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4709,22 +4783,22 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="H106" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4742,7 +4816,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4751,13 +4825,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4775,22 +4849,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4823,7 +4897,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4835,28 +4909,30 @@
         <v>16</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>19</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
+      <c t="s" r="M110" s="7">
+        <v>187</v>
+      </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c t="s" r="A111" s="6">
         <v>13</v>
       </c>
       <c t="s" r="B111" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c t="s" r="C111" s="7">
         <v>14</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4865,20 +4941,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="K111" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -4886,36 +4962,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B112" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="K112" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -4945,22 +5021,22 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4978,7 +5054,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -4987,13 +5063,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H115" s="8">
+        <v>195</v>
+      </c>
+      <c t="s" r="I115" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="J115" s="7">
         <v>190</v>
-      </c>
-      <c t="s" r="I115" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="J115" s="7">
-        <v>185</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5011,22 +5087,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5044,7 +5120,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5053,13 +5129,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5092,7 +5168,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5104,14 +5180,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>45</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
-      <c r="M119" s="7"/>
+      <c t="s" r="M119" s="7">
+        <v>199</v>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c t="s" r="A120" s="6">
@@ -5125,7 +5203,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5137,10 +5215,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5158,7 +5236,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5167,10 +5245,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>38</v>
@@ -5191,22 +5269,22 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5224,7 +5302,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5233,13 +5311,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5257,22 +5335,22 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5305,7 +5383,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5317,10 +5395,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5338,7 +5416,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5347,10 +5425,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>24</v>
@@ -5371,22 +5449,22 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5404,7 +5482,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5413,10 +5491,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>51</v>
@@ -5437,22 +5515,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5485,7 +5563,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5494,17 +5572,19 @@
         <v>50</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
+      <c t="s" r="M132" s="7">
+        <v>215</v>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c t="s" r="A133" s="6">
@@ -5518,19 +5598,19 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>25</v>
@@ -5551,7 +5631,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5560,13 +5640,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5584,22 +5664,22 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5628,30 +5708,32 @@
         <v>7615</v>
       </c>
       <c t="s" r="C137" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
+      <c t="s" r="M137" s="7">
+        <v>222</v>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c t="s" r="A138" s="6">
@@ -5661,11 +5743,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C138" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5677,10 +5759,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5698,7 +5780,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5710,10 +5792,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5746,13 +5828,13 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
@@ -5761,7 +5843,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5779,7 +5861,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5788,13 +5870,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5812,13 +5894,13 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>16</v>
@@ -5827,7 +5909,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5845,7 +5927,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5857,10 +5939,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5886,14 +5968,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B146" s="7">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c t="s" r="C146" s="7">
         <v>14</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5902,16 +5984,16 @@
         <v>22</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>25</v>
       </c>
       <c t="s" r="K146" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
@@ -5923,32 +6005,32 @@
         <v>13</v>
       </c>
       <c t="s" r="B147" s="7">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c t="s" r="C147" s="7">
         <v>14</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>28</v>
       </c>
       <c t="s" r="K147" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
@@ -5982,22 +6064,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6015,7 +6097,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6024,13 +6106,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6063,7 +6145,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6072,10 +6154,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>20</v>
@@ -6096,22 +6178,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6129,7 +6211,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6138,13 +6220,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6162,22 +6244,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6195,7 +6277,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6204,13 +6286,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6228,22 +6310,22 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6276,7 +6358,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6285,17 +6367,19 @@
         <v>50</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
-      <c r="M159" s="7"/>
+      <c t="s" r="M159" s="7">
+        <v>247</v>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c t="s" r="A160" s="6">
@@ -6309,22 +6393,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6342,19 +6426,19 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>39</v>
@@ -6375,22 +6459,22 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6423,7 +6507,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6432,17 +6516,19 @@
         <v>22</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
-      <c r="M164" s="7"/>
+      <c t="s" r="M164" s="7">
+        <v>252</v>
+      </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c t="s" r="A165" s="6">
@@ -6456,22 +6542,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>34</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6489,22 +6575,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6522,22 +6608,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6555,7 +6641,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6564,13 +6650,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6588,22 +6674,22 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6621,7 +6707,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6630,13 +6716,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6654,19 +6740,19 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>51</v>
@@ -6702,7 +6788,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6714,7 +6800,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>49</v>
@@ -6735,7 +6821,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6744,13 +6830,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6768,22 +6854,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6801,7 +6887,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6810,13 +6896,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6834,22 +6920,22 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6867,7 +6953,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6879,7 +6965,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>45</v>
@@ -6915,7 +7001,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6927,14 +7013,16 @@
         <v>22</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
-      <c r="M180" s="7"/>
+      <c t="s" r="M180" s="7">
+        <v>263</v>
+      </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c t="s" r="A181" s="6">
@@ -6948,7 +7036,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6960,10 +7048,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6981,7 +7069,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -6996,7 +7084,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7014,7 +7102,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7026,10 +7114,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7047,7 +7135,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7059,10 +7147,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7080,7 +7168,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7089,13 +7177,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7128,7 +7216,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7137,17 +7225,19 @@
         <v>22</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
-      <c r="M187" s="7"/>
+      <c t="s" r="M187" s="7">
+        <v>271</v>
+      </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c t="s" r="A188" s="6">
@@ -7161,22 +7251,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7194,7 +7284,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7203,13 +7293,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7227,13 +7317,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>22</v>
@@ -7242,7 +7332,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7260,7 +7350,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7269,13 +7359,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7293,22 +7383,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7341,22 +7431,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7374,7 +7464,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7383,13 +7473,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7407,22 +7497,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7440,19 +7530,19 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>40</v>
@@ -7473,7 +7563,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7482,13 +7572,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7521,7 +7611,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7530,17 +7620,19 @@
         <v>22</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
+      <c t="s" r="M200" s="7">
+        <v>280</v>
+      </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c t="s" r="A201" s="6">
@@ -7554,22 +7646,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7587,7 +7679,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7596,13 +7688,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7620,22 +7712,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7653,7 +7745,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7662,13 +7754,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7686,22 +7778,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7719,7 +7811,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7731,10 +7823,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7752,7 +7844,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7764,10 +7856,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7800,7 +7892,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7812,10 +7904,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7833,7 +7925,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7845,10 +7937,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7866,7 +7958,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7878,10 +7970,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7914,7 +8006,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7926,14 +8018,16 @@
         <v>22</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
-      <c r="M213" s="7"/>
+      <c t="s" r="M213" s="7">
+        <v>288</v>
+      </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
@@ -7947,7 +8041,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -7959,10 +8053,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7980,7 +8074,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -7992,7 +8086,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>49</v>
@@ -8013,7 +8107,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8022,13 +8116,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8046,22 +8140,22 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8094,7 +8188,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8103,17 +8197,19 @@
         <v>22</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
-      <c r="M219" s="7"/>
+      <c t="s" r="M219" s="7">
+        <v>296</v>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1">
       <c t="s" r="A220" s="6">
@@ -8127,22 +8223,22 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8160,7 +8256,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8172,10 +8268,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8193,7 +8289,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8205,10 +8301,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8226,7 +8322,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8238,10 +8334,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8259,7 +8355,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8268,13 +8364,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8292,22 +8388,22 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8340,7 +8436,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8349,17 +8445,19 @@
         <v>22</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
-      <c r="M227" s="7"/>
+      <c t="s" r="M227" s="7">
+        <v>92</v>
+      </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c t="s" r="A228" s="6">
@@ -8373,22 +8471,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8406,7 +8504,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8415,13 +8513,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8439,13 +8537,13 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>22</v>
@@ -8454,7 +8552,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8472,7 +8570,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8481,13 +8579,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8505,22 +8603,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8538,7 +8636,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8547,13 +8645,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8571,22 +8669,22 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8619,7 +8717,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8628,10 +8726,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>21</v>
@@ -8652,13 +8750,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>22</v>
@@ -8667,7 +8765,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8685,7 +8783,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8694,13 +8792,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8718,22 +8816,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8766,13 +8864,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>22</v>
@@ -8781,7 +8879,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8799,7 +8897,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8808,13 +8906,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8832,22 +8930,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8865,7 +8963,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8874,13 +8972,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8898,22 +8996,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8931,7 +9029,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -8943,10 +9041,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8979,7 +9077,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -8988,13 +9086,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9012,22 +9110,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9045,7 +9143,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9057,7 +9155,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>23</v>
@@ -9078,7 +9176,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9090,10 +9188,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9111,7 +9209,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9120,13 +9218,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9144,22 +9242,22 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9192,7 +9290,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9201,17 +9299,19 @@
         <v>22</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
-      <c r="M255" s="7"/>
+      <c t="s" r="M255" s="7">
+        <v>322</v>
+      </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
       <c t="s" r="A256" s="6">
@@ -9225,22 +9325,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9258,7 +9358,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9267,13 +9367,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9291,22 +9391,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9324,7 +9424,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9336,10 +9436,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9357,7 +9457,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9369,10 +9469,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9405,7 +9505,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
@@ -9414,13 +9514,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9438,22 +9538,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9471,7 +9571,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9483,10 +9583,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9504,7 +9604,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -9516,10 +9616,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9537,7 +9637,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -9546,13 +9646,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9570,22 +9670,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9603,7 +9703,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -9612,10 +9712,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>20</v>
@@ -9651,7 +9751,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9666,7 +9766,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9684,7 +9784,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9696,10 +9796,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9717,7 +9817,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9732,7 +9832,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9765,7 +9865,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9777,10 +9877,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9798,7 +9898,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9810,10 +9910,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9831,7 +9931,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -9840,10 +9940,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>38</v>
@@ -9864,22 +9964,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9897,7 +9997,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -9906,13 +10006,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9930,22 +10030,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9978,13 +10078,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>22</v>
@@ -9993,11 +10093,13 @@
         <v>52</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
-      <c r="M281" s="7"/>
+      <c t="s" r="M281" s="7">
+        <v>340</v>
+      </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
       <c t="s" r="A282" s="6">
@@ -10011,7 +10113,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10020,13 +10122,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10044,22 +10146,22 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10077,7 +10179,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10086,13 +10188,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10110,22 +10212,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10143,22 +10245,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10191,7 +10293,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10200,10 +10302,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>48</v>
@@ -10224,22 +10326,22 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10257,7 +10359,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10269,7 +10371,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>38</v>
@@ -10290,7 +10392,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10302,10 +10404,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10323,7 +10425,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10332,13 +10434,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10356,22 +10458,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10404,7 +10506,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10413,17 +10515,19 @@
         <v>22</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>32</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
-      <c r="M295" s="7"/>
+      <c t="s" r="M295" s="7">
+        <v>346</v>
+      </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
       <c t="s" r="A296" s="6">
@@ -10437,13 +10541,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>22</v>
@@ -10452,7 +10556,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10470,7 +10574,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10479,13 +10583,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10503,22 +10607,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10536,7 +10640,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10545,13 +10649,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10569,22 +10673,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
+        <v>344</v>
+      </c>
+      <c t="s" r="H300" s="8">
+        <v>22</v>
+      </c>
+      <c t="s" r="I300" s="7">
         <v>328</v>
       </c>
-      <c t="s" r="H300" s="8">
-        <v>22</v>
-      </c>
-      <c t="s" r="I300" s="7">
-        <v>313</v>
-      </c>
       <c t="s" r="J300" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10602,7 +10706,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10611,13 +10715,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10635,22 +10739,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10683,22 +10787,22 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10716,22 +10820,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10749,22 +10853,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10782,7 +10886,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10791,10 +10895,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>39</v>
@@ -10830,7 +10934,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -10842,14 +10946,16 @@
         <v>47</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
-      <c r="M309" s="7"/>
+      <c t="s" r="M309" s="7">
+        <v>353</v>
+      </c>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c t="s" r="A310" s="6">
@@ -10863,7 +10969,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10875,10 +10981,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10896,7 +11002,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -10905,13 +11011,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10929,22 +11035,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10962,7 +11068,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -10971,13 +11077,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10995,22 +11101,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11043,7 +11149,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11052,7 +11158,7 @@
         <v>22</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="I316" s="7">
         <v>52</v>
@@ -11062,7 +11168,9 @@
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
-      <c r="M316" s="7"/>
+      <c t="s" r="M316" s="7">
+        <v>92</v>
+      </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
       <c t="s" r="A317" s="6">
@@ -11076,22 +11184,22 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11109,7 +11217,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11118,13 +11226,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11142,22 +11250,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11175,7 +11283,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11184,13 +11292,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11208,22 +11316,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11241,7 +11349,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11250,13 +11358,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>26</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11274,22 +11382,22 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11322,7 +11430,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11331,13 +11439,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11355,13 +11463,13 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>16</v>
@@ -11370,7 +11478,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11388,7 +11496,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11400,10 +11508,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11421,7 +11529,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11433,10 +11541,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11454,7 +11562,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11466,10 +11574,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11502,7 +11610,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11514,10 +11622,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11535,7 +11643,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11547,7 +11655,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>49</v>
@@ -11568,7 +11676,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11580,7 +11688,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>25</v>
@@ -11601,7 +11709,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11610,13 +11718,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11634,22 +11742,22 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11682,7 +11790,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11691,13 +11799,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11715,22 +11823,22 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11748,7 +11856,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11757,13 +11865,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11781,19 +11889,19 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>24</v>
@@ -11814,7 +11922,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11823,13 +11931,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11847,22 +11955,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11880,7 +11988,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11889,13 +11997,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>28</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11913,22 +12021,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11961,7 +12069,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -11970,13 +12078,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>346</v>
+        <v>137</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11994,22 +12102,22 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12027,7 +12135,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12036,13 +12144,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12060,22 +12168,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12093,7 +12201,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12102,13 +12210,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12126,22 +12234,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12174,7 +12282,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12183,17 +12291,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
-      <c r="M353" s="7"/>
+      <c t="s" r="M353" s="7">
+        <v>367</v>
+      </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
       <c t="s" r="A354" s="6">
@@ -12207,22 +12317,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12240,7 +12350,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12252,10 +12362,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12273,7 +12383,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12285,10 +12395,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12306,7 +12416,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12315,13 +12425,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12339,22 +12449,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12372,7 +12482,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12381,13 +12491,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12405,22 +12515,22 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12453,7 +12563,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12462,13 +12572,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12486,22 +12596,22 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12519,22 +12629,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
+        <v>268</v>
+      </c>
+      <c t="s" r="H364" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="I364" s="7">
+        <v>114</v>
+      </c>
+      <c t="s" r="J364" s="7">
         <v>258</v>
-      </c>
-      <c t="s" r="H364" s="8">
-        <v>55</v>
-      </c>
-      <c t="s" r="I364" s="7">
-        <v>113</v>
-      </c>
-      <c t="s" r="J364" s="7">
-        <v>249</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12552,22 +12662,22 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12600,7 +12710,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12612,10 +12722,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12633,7 +12743,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12645,10 +12755,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12666,7 +12776,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12681,7 +12791,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12699,7 +12809,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12711,10 +12821,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12747,7 +12857,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12756,13 +12866,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12780,22 +12890,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12813,22 +12923,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12846,13 +12956,13 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>16</v>
@@ -12861,7 +12971,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12879,7 +12989,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12888,13 +12998,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12912,22 +13022,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12960,7 +13070,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -12972,10 +13082,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12993,7 +13103,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13002,13 +13112,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13026,22 +13136,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13059,7 +13169,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13071,10 +13181,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13092,7 +13202,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13104,10 +13214,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13140,22 +13250,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13173,22 +13283,22 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I386" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13206,22 +13316,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13239,22 +13349,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13287,7 +13397,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13296,13 +13406,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="I390" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13320,19 +13430,19 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>24</v>
@@ -13353,7 +13463,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13362,13 +13472,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13386,22 +13496,22 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13419,7 +13529,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13428,13 +13538,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13467,7 +13577,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13476,13 +13586,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13500,22 +13610,22 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13533,22 +13643,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13566,22 +13676,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13614,7 +13724,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13623,13 +13733,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13647,22 +13757,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13680,7 +13790,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13689,13 +13799,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13713,22 +13823,22 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13746,7 +13856,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13755,13 +13865,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13779,22 +13889,22 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13827,7 +13937,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -13836,10 +13946,10 @@
         <v>22</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>370</v>
+        <v>222</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>54</v>
@@ -13860,22 +13970,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>346</v>
+        <v>137</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13893,7 +14003,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -13902,13 +14012,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13926,22 +14036,22 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13959,7 +14069,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -13968,13 +14078,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13992,22 +14102,22 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14040,7 +14150,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14052,10 +14162,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14073,7 +14183,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14082,13 +14192,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14106,13 +14216,13 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>22</v>
@@ -14121,7 +14231,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14154,7 +14264,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14163,13 +14273,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14187,22 +14297,22 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14220,7 +14330,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14229,13 +14339,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14268,7 +14378,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14277,17 +14387,19 @@
         <v>22</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
-      <c r="M423" s="7"/>
+      <c t="s" r="M423" s="7">
+        <v>144</v>
+      </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
       <c t="s" r="A424" s="6">
@@ -14301,22 +14413,22 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>370</v>
+        <v>222</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14334,7 +14446,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14343,13 +14455,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14367,22 +14479,22 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14400,7 +14512,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14409,13 +14521,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14433,19 +14545,19 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>29</v>
@@ -14481,7 +14593,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -14490,13 +14602,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>370</v>
+        <v>222</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14514,13 +14626,13 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>22</v>
@@ -14529,7 +14641,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14547,7 +14659,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -14559,10 +14671,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14580,7 +14692,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -14595,7 +14707,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14613,7 +14725,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
@@ -14622,13 +14734,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14646,22 +14758,22 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14694,7 +14806,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -14706,14 +14818,16 @@
         <v>47</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
-      <c r="M437" s="7"/>
+      <c t="s" r="M437" s="7">
+        <v>395</v>
+      </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
       <c t="s" r="A438" s="6">
@@ -14727,7 +14841,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
@@ -14736,10 +14850,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>25</v>
@@ -14760,22 +14874,22 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14808,7 +14922,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
@@ -14817,13 +14931,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -14852,11 +14966,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C443" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
@@ -14865,13 +14979,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14885,26 +14999,26 @@
         <v>5806</v>
       </c>
       <c t="s" r="C444" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -14937,22 +15051,22 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -14970,7 +15084,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -14982,7 +15096,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>26</v>
@@ -15003,7 +15117,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
@@ -15012,13 +15126,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15051,7 +15165,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -15063,7 +15177,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>19</v>
@@ -15084,7 +15198,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -15093,13 +15207,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15117,22 +15231,22 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15165,7 +15279,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15174,13 +15288,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15198,22 +15312,22 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c t="s" r="H455" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15221,7 +15335,7 @@
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c t="s" r="A456" s="9">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="B456" s="9"/>
       <c r="C456" s="9"/>
@@ -15241,7 +15355,7 @@
     <row r="457" ht="65.25" customHeight="1"/>
     <row r="458" ht="16.5" customHeight="1">
       <c t="s" r="A458" s="10">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B458" s="10"/>
       <c r="C458" s="10"/>
@@ -15254,7 +15368,7 @@
       <c r="J458" s="10"/>
       <c r="K458" s="10"/>
       <c t="s" r="L458" s="11">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="M458" s="11"/>
       <c r="N458" s="11"/>
